--- a/omicron/xlsx/869-MTR-test-plan.xlsx
+++ b/omicron/xlsx/869-MTR-test-plan.xlsx
@@ -646,7 +646,7 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>generated 2026-09-05 12:27 from 869.html</t>
+          <t>generated 2026-09-15 01:22 from src/869-mtr.html</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1246,7 @@
       </c>
       <c r="F4" s="11" t="inlineStr">
         <is>
-          <t>Timing at 1.50 ×FLA</t>
+          <t>Timing at 1.5 ×FLA</t>
         </is>
       </c>
       <c r="G4" s="11" t="inlineStr">
@@ -1334,7 +1334,7 @@
       </c>
       <c r="F5" s="11" t="inlineStr">
         <is>
-          <t>Timing at 2.00 ×FLA</t>
+          <t>Timing at 2 ×FLA</t>
         </is>
       </c>
       <c r="G5" s="11" t="inlineStr">
@@ -1422,7 +1422,7 @@
       </c>
       <c r="F6" s="11" t="inlineStr">
         <is>
-          <t>Timing at 3.00 ×FLA</t>
+          <t>Timing at 3 ×FLA</t>
         </is>
       </c>
       <c r="G6" s="11" t="inlineStr">
@@ -1510,7 +1510,7 @@
       </c>
       <c r="F7" s="11" t="inlineStr">
         <is>
-          <t>Timing at 4.00 ×FLA</t>
+          <t>Timing at 4 ×FLA</t>
         </is>
       </c>
       <c r="G7" s="11" t="inlineStr">
@@ -1598,7 +1598,7 @@
       </c>
       <c r="F8" s="11" t="inlineStr">
         <is>
-          <t>Timing at 6.00 ×FLA</t>
+          <t>Timing at 6 ×FLA</t>
         </is>
       </c>
       <c r="G8" s="11" t="inlineStr">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="F9" s="14" t="inlineStr">
         <is>
-          <t>Accumulate at 2.0 ×FLA</t>
+          <t>Accumulate at 2 ×FLA</t>
         </is>
       </c>
       <c r="G9" s="14" t="inlineStr">
@@ -1774,7 +1774,7 @@
       </c>
       <c r="F10" s="14" t="inlineStr">
         <is>
-          <t>Accumulate at 4.0 ×FLA</t>
+          <t>Accumulate at 4 ×FLA</t>
         </is>
       </c>
       <c r="G10" s="14" t="inlineStr">
@@ -1862,7 +1862,7 @@
       </c>
       <c r="F11" s="14" t="inlineStr">
         <is>
-          <t>Accumulate at 6.0 ×FLA</t>
+          <t>Accumulate at 6 ×FLA</t>
         </is>
       </c>
       <c r="G11" s="14" t="inlineStr">
@@ -2403,7 +2403,7 @@
       </c>
       <c r="G17" s="11" t="inlineStr">
         <is>
-          <t>Current stepped to 6.00 ×FLA and held for the nameplate acceleration time of 8.00 s</t>
+          <t>Current stepped to 6 ×FLA and held for the nameplate acceleration time of 8.00 s</t>
         </is>
       </c>
       <c r="H17" s="12" t="n">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="G20" s="11" t="inlineStr">
         <is>
-          <t>Current held at 6.00 ×FLA past the 10.0 s limit — the motor never accelerates</t>
+          <t>Current held at 6 ×FLA past the 10.0 s limit — the motor never accelerates</t>
         </is>
       </c>
       <c r="H20" s="12" t="n">
@@ -4095,7 +4095,7 @@
       </c>
       <c r="G35" s="14" t="inlineStr">
         <is>
-          <t>I2/I1 = 16.5% · L3 reduced to 57.5% · Ieq 0.926 ×FLA</t>
+          <t>Relay sees 16.5% as I2/FLA · L3 reduced to 50.5% · I2/I1 19.8% · Ieq 0.928 ×FLA</t>
         </is>
       </c>
       <c r="H35" s="15" t="n"/>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="P35" s="15" t="inlineStr">
         <is>
-          <t>2.5880@92.9</t>
+          <t>2.2725@92.9</t>
         </is>
       </c>
       <c r="Q35" s="15" t="n">
@@ -4183,7 +4183,7 @@
       </c>
       <c r="G36" s="14" t="inlineStr">
         <is>
-          <t>I2/I1 = 13.5% · L3 reduced to 64.3% · Ieq 0.928 ×FLA</t>
+          <t>Relay sees 13.5% as I2/FLA · L3 reduced to 59.5% · I2/I1 15.6% · Ieq 0.926 ×FLA</t>
         </is>
       </c>
       <c r="H36" s="15" t="n"/>
@@ -4216,7 +4216,7 @@
       </c>
       <c r="P36" s="15" t="inlineStr">
         <is>
-          <t>2.8943@92.9</t>
+          <t>2.6775@92.9</t>
         </is>
       </c>
       <c r="Q36" s="15" t="n">
@@ -4271,7 +4271,7 @@
       </c>
       <c r="G37" s="14" t="inlineStr">
         <is>
-          <t>I2/I1 = 10.0% · below the trip ratio</t>
+          <t>Relay sees 10.0% as I2/FLA · below the trip ratio</t>
         </is>
       </c>
       <c r="H37" s="15" t="n"/>
@@ -4304,7 +4304,7 @@
       </c>
       <c r="P37" s="15" t="inlineStr">
         <is>
-          <t>3.2727@92.9</t>
+          <t>3.1500@92.9</t>
         </is>
       </c>
       <c r="Q37" s="15" t="n">
@@ -4359,7 +4359,7 @@
       </c>
       <c r="G38" s="14" t="inlineStr">
         <is>
-          <t>L3 taken to zero — the deepest a single open phase can go</t>
+          <t>L3 taken to zero — the deepest a single open phase can go at this load; the relay sees 33.3% (I2/FLA)</t>
         </is>
       </c>
       <c r="H38" s="15" t="n"/>
@@ -4410,7 +4410,7 @@
       </c>
       <c r="T38" s="14" t="inlineStr">
         <is>
-          <t>I2/I1 = 50%, the ceiling for this method</t>
+          <t>Above the 15% setting</t>
         </is>
       </c>
       <c r="U38" s="13" t="n"/>
@@ -5047,7 +5047,7 @@
       </c>
       <c r="G46" s="14" t="inlineStr">
         <is>
-          <t>All three phase leads bundled through the window in the correct direction at 4.0 ×FLA</t>
+          <t>All three phase leads bundled through the window in the correct direction at 4 ×FLA</t>
         </is>
       </c>
       <c r="H46" s="15" t="n"/>
@@ -5306,7 +5306,7 @@
       </c>
       <c r="F49" s="11" t="inlineStr">
         <is>
-          <t>Timing at 2.0× pickup</t>
+          <t>Timing at 2× pickup</t>
         </is>
       </c>
       <c r="G49" s="11" t="inlineStr">
@@ -5570,7 +5570,7 @@
       </c>
       <c r="F52" s="14" t="inlineStr">
         <is>
-          <t>Timing at 2.0× pickup</t>
+          <t>Timing at 2× pickup</t>
         </is>
       </c>
       <c r="G52" s="14" t="inlineStr">
@@ -5834,7 +5834,7 @@
       </c>
       <c r="F55" s="11" t="inlineStr">
         <is>
-          <t>Timing at 2.0× pickup</t>
+          <t>Timing at 2× pickup</t>
         </is>
       </c>
       <c r="G55" s="11" t="inlineStr">
@@ -5922,7 +5922,7 @@
       </c>
       <c r="F56" s="11" t="inlineStr">
         <is>
-          <t>Timing at 3.0× pickup</t>
+          <t>Timing at 3× pickup</t>
         </is>
       </c>
       <c r="G56" s="11" t="inlineStr">
@@ -6010,7 +6010,7 @@
       </c>
       <c r="F57" s="11" t="inlineStr">
         <is>
-          <t>Timing at 5.0× pickup</t>
+          <t>Timing at 5× pickup</t>
         </is>
       </c>
       <c r="G57" s="11" t="inlineStr">
@@ -6274,7 +6274,7 @@
       </c>
       <c r="F60" s="14" t="inlineStr">
         <is>
-          <t>Timing at 2.0× pickup</t>
+          <t>Timing at 2× pickup</t>
         </is>
       </c>
       <c r="G60" s="14" t="inlineStr">
@@ -6978,7 +6978,7 @@
       </c>
       <c r="F68" s="14" t="inlineStr">
         <is>
-          <t>Timing at 0.50× pickup</t>
+          <t>Timing at 0.5× pickup</t>
         </is>
       </c>
       <c r="G68" s="14" t="inlineStr">
@@ -10344,7 +10344,7 @@
       </c>
       <c r="G14" s="11" t="inlineStr">
         <is>
-          <t>Timing at 1.50 ×FLA</t>
+          <t>Timing at 1.5 ×FLA</t>
         </is>
       </c>
       <c r="H14" s="12" t="n"/>
@@ -10418,7 +10418,7 @@
       </c>
       <c r="G15" s="11" t="inlineStr">
         <is>
-          <t>Timing at 1.50 ×FLA</t>
+          <t>Timing at 1.5 ×FLA</t>
         </is>
       </c>
       <c r="H15" s="12" t="n"/>
@@ -10492,7 +10492,7 @@
       </c>
       <c r="G16" s="11" t="inlineStr">
         <is>
-          <t>Timing at 1.50 ×FLA</t>
+          <t>Timing at 1.5 ×FLA</t>
         </is>
       </c>
       <c r="H16" s="12" t="n"/>
@@ -10566,7 +10566,7 @@
       </c>
       <c r="G17" s="11" t="inlineStr">
         <is>
-          <t>Timing at 1.50 ×FLA</t>
+          <t>Timing at 1.5 ×FLA</t>
         </is>
       </c>
       <c r="H17" s="12" t="n"/>
@@ -10640,7 +10640,7 @@
       </c>
       <c r="G18" s="11" t="inlineStr">
         <is>
-          <t>Timing at 1.50 ×FLA</t>
+          <t>Timing at 1.5 ×FLA</t>
         </is>
       </c>
       <c r="H18" s="12" t="n"/>
@@ -10714,7 +10714,7 @@
       </c>
       <c r="G19" s="11" t="inlineStr">
         <is>
-          <t>Timing at 1.50 ×FLA</t>
+          <t>Timing at 1.5 ×FLA</t>
         </is>
       </c>
       <c r="H19" s="12" t="n"/>
@@ -10788,7 +10788,7 @@
       </c>
       <c r="G20" s="11" t="inlineStr">
         <is>
-          <t>Timing at 2.00 ×FLA</t>
+          <t>Timing at 2 ×FLA</t>
         </is>
       </c>
       <c r="H20" s="12" t="n"/>
@@ -10862,7 +10862,7 @@
       </c>
       <c r="G21" s="11" t="inlineStr">
         <is>
-          <t>Timing at 2.00 ×FLA</t>
+          <t>Timing at 2 ×FLA</t>
         </is>
       </c>
       <c r="H21" s="12" t="n"/>
@@ -10936,7 +10936,7 @@
       </c>
       <c r="G22" s="11" t="inlineStr">
         <is>
-          <t>Timing at 2.00 ×FLA</t>
+          <t>Timing at 2 ×FLA</t>
         </is>
       </c>
       <c r="H22" s="12" t="n"/>
@@ -11010,7 +11010,7 @@
       </c>
       <c r="G23" s="11" t="inlineStr">
         <is>
-          <t>Timing at 2.00 ×FLA</t>
+          <t>Timing at 2 ×FLA</t>
         </is>
       </c>
       <c r="H23" s="12" t="n"/>
@@ -11084,7 +11084,7 @@
       </c>
       <c r="G24" s="11" t="inlineStr">
         <is>
-          <t>Timing at 2.00 ×FLA</t>
+          <t>Timing at 2 ×FLA</t>
         </is>
       </c>
       <c r="H24" s="12" t="n"/>
@@ -11158,7 +11158,7 @@
       </c>
       <c r="G25" s="11" t="inlineStr">
         <is>
-          <t>Timing at 2.00 ×FLA</t>
+          <t>Timing at 2 ×FLA</t>
         </is>
       </c>
       <c r="H25" s="12" t="n"/>
@@ -11232,7 +11232,7 @@
       </c>
       <c r="G26" s="11" t="inlineStr">
         <is>
-          <t>Timing at 3.00 ×FLA</t>
+          <t>Timing at 3 ×FLA</t>
         </is>
       </c>
       <c r="H26" s="12" t="n"/>
@@ -11306,7 +11306,7 @@
       </c>
       <c r="G27" s="11" t="inlineStr">
         <is>
-          <t>Timing at 3.00 ×FLA</t>
+          <t>Timing at 3 ×FLA</t>
         </is>
       </c>
       <c r="H27" s="12" t="n"/>
@@ -11380,7 +11380,7 @@
       </c>
       <c r="G28" s="11" t="inlineStr">
         <is>
-          <t>Timing at 3.00 ×FLA</t>
+          <t>Timing at 3 ×FLA</t>
         </is>
       </c>
       <c r="H28" s="12" t="n"/>
@@ -11454,7 +11454,7 @@
       </c>
       <c r="G29" s="11" t="inlineStr">
         <is>
-          <t>Timing at 3.00 ×FLA</t>
+          <t>Timing at 3 ×FLA</t>
         </is>
       </c>
       <c r="H29" s="12" t="n"/>
@@ -11528,7 +11528,7 @@
       </c>
       <c r="G30" s="11" t="inlineStr">
         <is>
-          <t>Timing at 3.00 ×FLA</t>
+          <t>Timing at 3 ×FLA</t>
         </is>
       </c>
       <c r="H30" s="12" t="n"/>
@@ -11602,7 +11602,7 @@
       </c>
       <c r="G31" s="11" t="inlineStr">
         <is>
-          <t>Timing at 3.00 ×FLA</t>
+          <t>Timing at 3 ×FLA</t>
         </is>
       </c>
       <c r="H31" s="12" t="n"/>
@@ -11676,7 +11676,7 @@
       </c>
       <c r="G32" s="11" t="inlineStr">
         <is>
-          <t>Timing at 4.00 ×FLA</t>
+          <t>Timing at 4 ×FLA</t>
         </is>
       </c>
       <c r="H32" s="12" t="n"/>
@@ -11750,7 +11750,7 @@
       </c>
       <c r="G33" s="11" t="inlineStr">
         <is>
-          <t>Timing at 4.00 ×FLA</t>
+          <t>Timing at 4 ×FLA</t>
         </is>
       </c>
       <c r="H33" s="12" t="n"/>
@@ -11824,7 +11824,7 @@
       </c>
       <c r="G34" s="11" t="inlineStr">
         <is>
-          <t>Timing at 4.00 ×FLA</t>
+          <t>Timing at 4 ×FLA</t>
         </is>
       </c>
       <c r="H34" s="12" t="n"/>
@@ -11898,7 +11898,7 @@
       </c>
       <c r="G35" s="11" t="inlineStr">
         <is>
-          <t>Timing at 4.00 ×FLA</t>
+          <t>Timing at 4 ×FLA</t>
         </is>
       </c>
       <c r="H35" s="12" t="n"/>
@@ -11972,7 +11972,7 @@
       </c>
       <c r="G36" s="11" t="inlineStr">
         <is>
-          <t>Timing at 4.00 ×FLA</t>
+          <t>Timing at 4 ×FLA</t>
         </is>
       </c>
       <c r="H36" s="12" t="n"/>
@@ -12046,7 +12046,7 @@
       </c>
       <c r="G37" s="11" t="inlineStr">
         <is>
-          <t>Timing at 4.00 ×FLA</t>
+          <t>Timing at 4 ×FLA</t>
         </is>
       </c>
       <c r="H37" s="12" t="n"/>
@@ -12120,7 +12120,7 @@
       </c>
       <c r="G38" s="11" t="inlineStr">
         <is>
-          <t>Timing at 6.00 ×FLA</t>
+          <t>Timing at 6 ×FLA</t>
         </is>
       </c>
       <c r="H38" s="12" t="n"/>
@@ -12194,7 +12194,7 @@
       </c>
       <c r="G39" s="11" t="inlineStr">
         <is>
-          <t>Timing at 6.00 ×FLA</t>
+          <t>Timing at 6 ×FLA</t>
         </is>
       </c>
       <c r="H39" s="12" t="n"/>
@@ -12268,7 +12268,7 @@
       </c>
       <c r="G40" s="11" t="inlineStr">
         <is>
-          <t>Timing at 6.00 ×FLA</t>
+          <t>Timing at 6 ×FLA</t>
         </is>
       </c>
       <c r="H40" s="12" t="n"/>
@@ -12342,7 +12342,7 @@
       </c>
       <c r="G41" s="11" t="inlineStr">
         <is>
-          <t>Timing at 6.00 ×FLA</t>
+          <t>Timing at 6 ×FLA</t>
         </is>
       </c>
       <c r="H41" s="12" t="n"/>
@@ -12416,7 +12416,7 @@
       </c>
       <c r="G42" s="11" t="inlineStr">
         <is>
-          <t>Timing at 6.00 ×FLA</t>
+          <t>Timing at 6 ×FLA</t>
         </is>
       </c>
       <c r="H42" s="12" t="n"/>
@@ -12490,7 +12490,7 @@
       </c>
       <c r="G43" s="11" t="inlineStr">
         <is>
-          <t>Timing at 6.00 ×FLA</t>
+          <t>Timing at 6 ×FLA</t>
         </is>
       </c>
       <c r="H43" s="12" t="n"/>
@@ -12564,7 +12564,7 @@
       </c>
       <c r="G44" s="14" t="inlineStr">
         <is>
-          <t>Accumulate at 2.0 ×FLA</t>
+          <t>Accumulate at 2 ×FLA</t>
         </is>
       </c>
       <c r="H44" s="15" t="n"/>
@@ -12638,7 +12638,7 @@
       </c>
       <c r="G45" s="14" t="inlineStr">
         <is>
-          <t>Accumulate at 2.0 ×FLA</t>
+          <t>Accumulate at 2 ×FLA</t>
         </is>
       </c>
       <c r="H45" s="15" t="n"/>
@@ -12712,7 +12712,7 @@
       </c>
       <c r="G46" s="14" t="inlineStr">
         <is>
-          <t>Accumulate at 2.0 ×FLA</t>
+          <t>Accumulate at 2 ×FLA</t>
         </is>
       </c>
       <c r="H46" s="15" t="n"/>
@@ -12786,7 +12786,7 @@
       </c>
       <c r="G47" s="14" t="inlineStr">
         <is>
-          <t>Accumulate at 2.0 ×FLA</t>
+          <t>Accumulate at 2 ×FLA</t>
         </is>
       </c>
       <c r="H47" s="15" t="n"/>
@@ -12860,7 +12860,7 @@
       </c>
       <c r="G48" s="14" t="inlineStr">
         <is>
-          <t>Accumulate at 2.0 ×FLA</t>
+          <t>Accumulate at 2 ×FLA</t>
         </is>
       </c>
       <c r="H48" s="15" t="n"/>
@@ -12934,7 +12934,7 @@
       </c>
       <c r="G49" s="14" t="inlineStr">
         <is>
-          <t>Accumulate at 2.0 ×FLA</t>
+          <t>Accumulate at 2 ×FLA</t>
         </is>
       </c>
       <c r="H49" s="15" t="n"/>
@@ -13008,7 +13008,7 @@
       </c>
       <c r="G50" s="14" t="inlineStr">
         <is>
-          <t>Accumulate at 4.0 ×FLA</t>
+          <t>Accumulate at 4 ×FLA</t>
         </is>
       </c>
       <c r="H50" s="15" t="n"/>
@@ -13082,7 +13082,7 @@
       </c>
       <c r="G51" s="14" t="inlineStr">
         <is>
-          <t>Accumulate at 4.0 ×FLA</t>
+          <t>Accumulate at 4 ×FLA</t>
         </is>
       </c>
       <c r="H51" s="15" t="n"/>
@@ -13156,7 +13156,7 @@
       </c>
       <c r="G52" s="14" t="inlineStr">
         <is>
-          <t>Accumulate at 4.0 ×FLA</t>
+          <t>Accumulate at 4 ×FLA</t>
         </is>
       </c>
       <c r="H52" s="15" t="n"/>
@@ -13230,7 +13230,7 @@
       </c>
       <c r="G53" s="14" t="inlineStr">
         <is>
-          <t>Accumulate at 4.0 ×FLA</t>
+          <t>Accumulate at 4 ×FLA</t>
         </is>
       </c>
       <c r="H53" s="15" t="n"/>
@@ -13304,7 +13304,7 @@
       </c>
       <c r="G54" s="14" t="inlineStr">
         <is>
-          <t>Accumulate at 4.0 ×FLA</t>
+          <t>Accumulate at 4 ×FLA</t>
         </is>
       </c>
       <c r="H54" s="15" t="n"/>
@@ -13378,7 +13378,7 @@
       </c>
       <c r="G55" s="14" t="inlineStr">
         <is>
-          <t>Accumulate at 4.0 ×FLA</t>
+          <t>Accumulate at 4 ×FLA</t>
         </is>
       </c>
       <c r="H55" s="15" t="n"/>
@@ -13452,7 +13452,7 @@
       </c>
       <c r="G56" s="14" t="inlineStr">
         <is>
-          <t>Accumulate at 6.0 ×FLA</t>
+          <t>Accumulate at 6 ×FLA</t>
         </is>
       </c>
       <c r="H56" s="15" t="n"/>
@@ -13526,7 +13526,7 @@
       </c>
       <c r="G57" s="14" t="inlineStr">
         <is>
-          <t>Accumulate at 6.0 ×FLA</t>
+          <t>Accumulate at 6 ×FLA</t>
         </is>
       </c>
       <c r="H57" s="15" t="n"/>
@@ -13600,7 +13600,7 @@
       </c>
       <c r="G58" s="14" t="inlineStr">
         <is>
-          <t>Accumulate at 6.0 ×FLA</t>
+          <t>Accumulate at 6 ×FLA</t>
         </is>
       </c>
       <c r="H58" s="15" t="n"/>
@@ -13674,7 +13674,7 @@
       </c>
       <c r="G59" s="14" t="inlineStr">
         <is>
-          <t>Accumulate at 6.0 ×FLA</t>
+          <t>Accumulate at 6 ×FLA</t>
         </is>
       </c>
       <c r="H59" s="15" t="n"/>
@@ -13748,7 +13748,7 @@
       </c>
       <c r="G60" s="14" t="inlineStr">
         <is>
-          <t>Accumulate at 6.0 ×FLA</t>
+          <t>Accumulate at 6 ×FLA</t>
         </is>
       </c>
       <c r="H60" s="15" t="n"/>
@@ -13822,7 +13822,7 @@
       </c>
       <c r="G61" s="14" t="inlineStr">
         <is>
-          <t>Accumulate at 6.0 ×FLA</t>
+          <t>Accumulate at 6 ×FLA</t>
         </is>
       </c>
       <c r="H61" s="15" t="n"/>
@@ -25547,7 +25547,7 @@
         </is>
       </c>
       <c r="M205" s="15" t="n">
-        <v>2.588</v>
+        <v>2.2725</v>
       </c>
       <c r="N205" s="15" t="inlineStr">
         <is>
@@ -25562,7 +25562,7 @@
       </c>
       <c r="Q205" s="14" t="inlineStr">
         <is>
-          <t>reduced to 57.5% of the others</t>
+          <t>reduced to 50.5% of the others</t>
         </is>
       </c>
       <c r="R205" s="14" t="inlineStr">
@@ -25995,7 +25995,7 @@
         </is>
       </c>
       <c r="M211" s="15" t="n">
-        <v>2.8943</v>
+        <v>2.6775</v>
       </c>
       <c r="N211" s="15" t="inlineStr">
         <is>
@@ -26010,7 +26010,7 @@
       </c>
       <c r="Q211" s="14" t="inlineStr">
         <is>
-          <t>reduced to 64.3% of the others</t>
+          <t>reduced to 59.5% of the others</t>
         </is>
       </c>
       <c r="R211" s="14" t="inlineStr">
@@ -26443,7 +26443,7 @@
         </is>
       </c>
       <c r="M217" s="15" t="n">
-        <v>3.2727</v>
+        <v>3.15</v>
       </c>
       <c r="N217" s="15" t="inlineStr">
         <is>
@@ -26458,7 +26458,7 @@
       </c>
       <c r="Q217" s="14" t="inlineStr">
         <is>
-          <t>reduced to 72.7% of the others</t>
+          <t>reduced to 70.0% of the others</t>
         </is>
       </c>
       <c r="R217" s="14" t="inlineStr">
@@ -26542,7 +26542,7 @@
       </c>
       <c r="S218" s="14" t="inlineStr">
         <is>
-          <t>I2/I1 = 50%, the ceiling for this method</t>
+          <t>Above the 15% setting</t>
         </is>
       </c>
       <c r="T218" s="15" t="inlineStr">
@@ -26616,7 +26616,7 @@
       </c>
       <c r="S219" s="14" t="inlineStr">
         <is>
-          <t>I2/I1 = 50%, the ceiling for this method</t>
+          <t>Above the 15% setting</t>
         </is>
       </c>
       <c r="T219" s="15" t="inlineStr">
@@ -26690,7 +26690,7 @@
       </c>
       <c r="S220" s="14" t="inlineStr">
         <is>
-          <t>I2/I1 = 50%, the ceiling for this method</t>
+          <t>Above the 15% setting</t>
         </is>
       </c>
       <c r="T220" s="15" t="inlineStr">
@@ -26764,7 +26764,7 @@
       </c>
       <c r="S221" s="14" t="inlineStr">
         <is>
-          <t>I2/I1 = 50%, the ceiling for this method</t>
+          <t>Above the 15% setting</t>
         </is>
       </c>
       <c r="T221" s="15" t="inlineStr">
@@ -26838,7 +26838,7 @@
       </c>
       <c r="S222" s="14" t="inlineStr">
         <is>
-          <t>I2/I1 = 50%, the ceiling for this method</t>
+          <t>Above the 15% setting</t>
         </is>
       </c>
       <c r="T222" s="15" t="inlineStr">
@@ -26916,7 +26916,7 @@
       </c>
       <c r="S223" s="14" t="inlineStr">
         <is>
-          <t>I2/I1 = 50%, the ceiling for this method</t>
+          <t>Above the 15% setting</t>
         </is>
       </c>
       <c r="T223" s="15" t="inlineStr">
@@ -31108,7 +31108,7 @@
       </c>
       <c r="G280" s="11" t="inlineStr">
         <is>
-          <t>Timing at 2.0× pickup</t>
+          <t>Timing at 2× pickup</t>
         </is>
       </c>
       <c r="H280" s="12" t="n"/>
@@ -31182,7 +31182,7 @@
       </c>
       <c r="G281" s="11" t="inlineStr">
         <is>
-          <t>Timing at 2.0× pickup</t>
+          <t>Timing at 2× pickup</t>
         </is>
       </c>
       <c r="H281" s="12" t="n"/>
@@ -31256,7 +31256,7 @@
       </c>
       <c r="G282" s="11" t="inlineStr">
         <is>
-          <t>Timing at 2.0× pickup</t>
+          <t>Timing at 2× pickup</t>
         </is>
       </c>
       <c r="H282" s="12" t="n"/>
@@ -31330,7 +31330,7 @@
       </c>
       <c r="G283" s="11" t="inlineStr">
         <is>
-          <t>Timing at 2.0× pickup</t>
+          <t>Timing at 2× pickup</t>
         </is>
       </c>
       <c r="H283" s="12" t="n"/>
@@ -31404,7 +31404,7 @@
       </c>
       <c r="G284" s="11" t="inlineStr">
         <is>
-          <t>Timing at 2.0× pickup</t>
+          <t>Timing at 2× pickup</t>
         </is>
       </c>
       <c r="H284" s="12" t="n"/>
@@ -31478,7 +31478,7 @@
       </c>
       <c r="G285" s="11" t="inlineStr">
         <is>
-          <t>Timing at 2.0× pickup</t>
+          <t>Timing at 2× pickup</t>
         </is>
       </c>
       <c r="H285" s="12" t="n"/>
@@ -31800,7 +31800,11 @@
       <c r="P289" s="15" t="n">
         <v>60</v>
       </c>
-      <c r="Q289" s="14" t="n"/>
+      <c r="Q289" s="14" t="inlineStr">
+        <is>
+          <t>into the ground CT input</t>
+        </is>
+      </c>
       <c r="R289" s="14" t="inlineStr">
         <is>
           <t>OPERATE</t>
@@ -32244,7 +32248,11 @@
       <c r="P295" s="15" t="n">
         <v>60</v>
       </c>
-      <c r="Q295" s="14" t="n"/>
+      <c r="Q295" s="14" t="inlineStr">
+        <is>
+          <t>into the ground CT input</t>
+        </is>
+      </c>
       <c r="R295" s="14" t="inlineStr">
         <is>
           <t>RESTRAIN</t>
@@ -32440,7 +32448,7 @@
       </c>
       <c r="G298" s="14" t="inlineStr">
         <is>
-          <t>Timing at 2.0× pickup</t>
+          <t>Timing at 2× pickup</t>
         </is>
       </c>
       <c r="H298" s="15" t="n"/>
@@ -32514,7 +32522,7 @@
       </c>
       <c r="G299" s="14" t="inlineStr">
         <is>
-          <t>Timing at 2.0× pickup</t>
+          <t>Timing at 2× pickup</t>
         </is>
       </c>
       <c r="H299" s="15" t="n"/>
@@ -32588,7 +32596,7 @@
       </c>
       <c r="G300" s="14" t="inlineStr">
         <is>
-          <t>Timing at 2.0× pickup</t>
+          <t>Timing at 2× pickup</t>
         </is>
       </c>
       <c r="H300" s="15" t="n"/>
@@ -32662,7 +32670,7 @@
       </c>
       <c r="G301" s="14" t="inlineStr">
         <is>
-          <t>Timing at 2.0× pickup</t>
+          <t>Timing at 2× pickup</t>
         </is>
       </c>
       <c r="H301" s="15" t="n"/>
@@ -32688,7 +32696,11 @@
       <c r="P301" s="15" t="n">
         <v>60</v>
       </c>
-      <c r="Q301" s="14" t="n"/>
+      <c r="Q301" s="14" t="inlineStr">
+        <is>
+          <t>into the ground CT input</t>
+        </is>
+      </c>
       <c r="R301" s="14" t="inlineStr">
         <is>
           <t>0.05 s</t>
@@ -32736,7 +32748,7 @@
       </c>
       <c r="G302" s="14" t="inlineStr">
         <is>
-          <t>Timing at 2.0× pickup</t>
+          <t>Timing at 2× pickup</t>
         </is>
       </c>
       <c r="H302" s="15" t="n"/>
@@ -32810,7 +32822,7 @@
       </c>
       <c r="G303" s="14" t="inlineStr">
         <is>
-          <t>Timing at 2.0× pickup</t>
+          <t>Timing at 2× pickup</t>
         </is>
       </c>
       <c r="H303" s="15" t="n"/>
@@ -33132,7 +33144,11 @@
       <c r="P307" s="12" t="n">
         <v>60</v>
       </c>
-      <c r="Q307" s="11" t="n"/>
+      <c r="Q307" s="11" t="inlineStr">
+        <is>
+          <t>into the ground CT input</t>
+        </is>
+      </c>
       <c r="R307" s="11" t="inlineStr">
         <is>
           <t>OPERATE</t>
@@ -33576,7 +33592,11 @@
       <c r="P313" s="12" t="n">
         <v>60</v>
       </c>
-      <c r="Q313" s="11" t="n"/>
+      <c r="Q313" s="11" t="inlineStr">
+        <is>
+          <t>into the ground CT input</t>
+        </is>
+      </c>
       <c r="R313" s="11" t="inlineStr">
         <is>
           <t>RESTRAIN</t>
@@ -33772,7 +33792,7 @@
       </c>
       <c r="G316" s="11" t="inlineStr">
         <is>
-          <t>Timing at 2.0× pickup</t>
+          <t>Timing at 2× pickup</t>
         </is>
       </c>
       <c r="H316" s="12" t="n"/>
@@ -33846,7 +33866,7 @@
       </c>
       <c r="G317" s="11" t="inlineStr">
         <is>
-          <t>Timing at 2.0× pickup</t>
+          <t>Timing at 2× pickup</t>
         </is>
       </c>
       <c r="H317" s="12" t="n"/>
@@ -33920,7 +33940,7 @@
       </c>
       <c r="G318" s="11" t="inlineStr">
         <is>
-          <t>Timing at 2.0× pickup</t>
+          <t>Timing at 2× pickup</t>
         </is>
       </c>
       <c r="H318" s="12" t="n"/>
@@ -33994,7 +34014,7 @@
       </c>
       <c r="G319" s="11" t="inlineStr">
         <is>
-          <t>Timing at 2.0× pickup</t>
+          <t>Timing at 2× pickup</t>
         </is>
       </c>
       <c r="H319" s="12" t="n"/>
@@ -34020,7 +34040,11 @@
       <c r="P319" s="12" t="n">
         <v>60</v>
       </c>
-      <c r="Q319" s="11" t="n"/>
+      <c r="Q319" s="11" t="inlineStr">
+        <is>
+          <t>into the ground CT input</t>
+        </is>
+      </c>
       <c r="R319" s="11" t="inlineStr">
         <is>
           <t>2.01 s</t>
@@ -34068,7 +34092,7 @@
       </c>
       <c r="G320" s="11" t="inlineStr">
         <is>
-          <t>Timing at 2.0× pickup</t>
+          <t>Timing at 2× pickup</t>
         </is>
       </c>
       <c r="H320" s="12" t="n"/>
@@ -34142,7 +34166,7 @@
       </c>
       <c r="G321" s="11" t="inlineStr">
         <is>
-          <t>Timing at 2.0× pickup</t>
+          <t>Timing at 2× pickup</t>
         </is>
       </c>
       <c r="H321" s="12" t="n"/>
@@ -34216,7 +34240,7 @@
       </c>
       <c r="G322" s="11" t="inlineStr">
         <is>
-          <t>Timing at 3.0× pickup</t>
+          <t>Timing at 3× pickup</t>
         </is>
       </c>
       <c r="H322" s="12" t="n"/>
@@ -34290,7 +34314,7 @@
       </c>
       <c r="G323" s="11" t="inlineStr">
         <is>
-          <t>Timing at 3.0× pickup</t>
+          <t>Timing at 3× pickup</t>
         </is>
       </c>
       <c r="H323" s="12" t="n"/>
@@ -34364,7 +34388,7 @@
       </c>
       <c r="G324" s="11" t="inlineStr">
         <is>
-          <t>Timing at 3.0× pickup</t>
+          <t>Timing at 3× pickup</t>
         </is>
       </c>
       <c r="H324" s="12" t="n"/>
@@ -34438,7 +34462,7 @@
       </c>
       <c r="G325" s="11" t="inlineStr">
         <is>
-          <t>Timing at 3.0× pickup</t>
+          <t>Timing at 3× pickup</t>
         </is>
       </c>
       <c r="H325" s="12" t="n"/>
@@ -34464,7 +34488,11 @@
       <c r="P325" s="12" t="n">
         <v>60</v>
       </c>
-      <c r="Q325" s="11" t="n"/>
+      <c r="Q325" s="11" t="inlineStr">
+        <is>
+          <t>into the ground CT input</t>
+        </is>
+      </c>
       <c r="R325" s="11" t="inlineStr">
         <is>
           <t>1.26 s</t>
@@ -34512,7 +34540,7 @@
       </c>
       <c r="G326" s="11" t="inlineStr">
         <is>
-          <t>Timing at 3.0× pickup</t>
+          <t>Timing at 3× pickup</t>
         </is>
       </c>
       <c r="H326" s="12" t="n"/>
@@ -34586,7 +34614,7 @@
       </c>
       <c r="G327" s="11" t="inlineStr">
         <is>
-          <t>Timing at 3.0× pickup</t>
+          <t>Timing at 3× pickup</t>
         </is>
       </c>
       <c r="H327" s="12" t="n"/>
@@ -34660,7 +34688,7 @@
       </c>
       <c r="G328" s="11" t="inlineStr">
         <is>
-          <t>Timing at 5.0× pickup</t>
+          <t>Timing at 5× pickup</t>
         </is>
       </c>
       <c r="H328" s="12" t="n"/>
@@ -34734,7 +34762,7 @@
       </c>
       <c r="G329" s="11" t="inlineStr">
         <is>
-          <t>Timing at 5.0× pickup</t>
+          <t>Timing at 5× pickup</t>
         </is>
       </c>
       <c r="H329" s="12" t="n"/>
@@ -34808,7 +34836,7 @@
       </c>
       <c r="G330" s="11" t="inlineStr">
         <is>
-          <t>Timing at 5.0× pickup</t>
+          <t>Timing at 5× pickup</t>
         </is>
       </c>
       <c r="H330" s="12" t="n"/>
@@ -34882,7 +34910,7 @@
       </c>
       <c r="G331" s="11" t="inlineStr">
         <is>
-          <t>Timing at 5.0× pickup</t>
+          <t>Timing at 5× pickup</t>
         </is>
       </c>
       <c r="H331" s="12" t="n"/>
@@ -34908,7 +34936,11 @@
       <c r="P331" s="12" t="n">
         <v>60</v>
       </c>
-      <c r="Q331" s="11" t="n"/>
+      <c r="Q331" s="11" t="inlineStr">
+        <is>
+          <t>into the ground CT input</t>
+        </is>
+      </c>
       <c r="R331" s="11" t="inlineStr">
         <is>
           <t>0.86 s</t>
@@ -34956,7 +34988,7 @@
       </c>
       <c r="G332" s="11" t="inlineStr">
         <is>
-          <t>Timing at 5.0× pickup</t>
+          <t>Timing at 5× pickup</t>
         </is>
       </c>
       <c r="H332" s="12" t="n"/>
@@ -35030,7 +35062,7 @@
       </c>
       <c r="G333" s="11" t="inlineStr">
         <is>
-          <t>Timing at 5.0× pickup</t>
+          <t>Timing at 5× pickup</t>
         </is>
       </c>
       <c r="H333" s="12" t="n"/>
@@ -35352,7 +35384,11 @@
       <c r="P337" s="15" t="n">
         <v>60</v>
       </c>
-      <c r="Q337" s="14" t="n"/>
+      <c r="Q337" s="14" t="inlineStr">
+        <is>
+          <t>through the core-balance CT window</t>
+        </is>
+      </c>
       <c r="R337" s="14" t="inlineStr">
         <is>
           <t>OPERATE</t>
@@ -35796,7 +35832,11 @@
       <c r="P343" s="15" t="n">
         <v>60</v>
       </c>
-      <c r="Q343" s="14" t="n"/>
+      <c r="Q343" s="14" t="inlineStr">
+        <is>
+          <t>through the core-balance CT window</t>
+        </is>
+      </c>
       <c r="R343" s="14" t="inlineStr">
         <is>
           <t>RESTRAIN</t>
@@ -35992,7 +36032,7 @@
       </c>
       <c r="G346" s="14" t="inlineStr">
         <is>
-          <t>Timing at 2.0× pickup</t>
+          <t>Timing at 2× pickup</t>
         </is>
       </c>
       <c r="H346" s="15" t="n"/>
@@ -36066,7 +36106,7 @@
       </c>
       <c r="G347" s="14" t="inlineStr">
         <is>
-          <t>Timing at 2.0× pickup</t>
+          <t>Timing at 2× pickup</t>
         </is>
       </c>
       <c r="H347" s="15" t="n"/>
@@ -36140,7 +36180,7 @@
       </c>
       <c r="G348" s="14" t="inlineStr">
         <is>
-          <t>Timing at 2.0× pickup</t>
+          <t>Timing at 2× pickup</t>
         </is>
       </c>
       <c r="H348" s="15" t="n"/>
@@ -36214,7 +36254,7 @@
       </c>
       <c r="G349" s="14" t="inlineStr">
         <is>
-          <t>Timing at 2.0× pickup</t>
+          <t>Timing at 2× pickup</t>
         </is>
       </c>
       <c r="H349" s="15" t="n"/>
@@ -36240,7 +36280,11 @@
       <c r="P349" s="15" t="n">
         <v>60</v>
       </c>
-      <c r="Q349" s="14" t="n"/>
+      <c r="Q349" s="14" t="inlineStr">
+        <is>
+          <t>through the core-balance CT window</t>
+        </is>
+      </c>
       <c r="R349" s="14" t="inlineStr">
         <is>
           <t>0.05 s</t>
@@ -36288,7 +36332,7 @@
       </c>
       <c r="G350" s="14" t="inlineStr">
         <is>
-          <t>Timing at 2.0× pickup</t>
+          <t>Timing at 2× pickup</t>
         </is>
       </c>
       <c r="H350" s="15" t="n"/>
@@ -36362,7 +36406,7 @@
       </c>
       <c r="G351" s="14" t="inlineStr">
         <is>
-          <t>Timing at 2.0× pickup</t>
+          <t>Timing at 2× pickup</t>
         </is>
       </c>
       <c r="H351" s="15" t="n"/>
@@ -39544,7 +39588,7 @@
       </c>
       <c r="G394" s="14" t="inlineStr">
         <is>
-          <t>Timing at 0.50× pickup</t>
+          <t>Timing at 0.5× pickup</t>
         </is>
       </c>
       <c r="H394" s="15" t="n"/>
@@ -39618,7 +39662,7 @@
       </c>
       <c r="G395" s="14" t="inlineStr">
         <is>
-          <t>Timing at 0.50× pickup</t>
+          <t>Timing at 0.5× pickup</t>
         </is>
       </c>
       <c r="H395" s="15" t="n"/>
@@ -39692,7 +39736,7 @@
       </c>
       <c r="G396" s="14" t="inlineStr">
         <is>
-          <t>Timing at 0.50× pickup</t>
+          <t>Timing at 0.5× pickup</t>
         </is>
       </c>
       <c r="H396" s="15" t="n"/>
@@ -39766,7 +39810,7 @@
       </c>
       <c r="G397" s="14" t="inlineStr">
         <is>
-          <t>Timing at 0.50× pickup</t>
+          <t>Timing at 0.5× pickup</t>
         </is>
       </c>
       <c r="H397" s="15" t="n"/>
@@ -39840,7 +39884,7 @@
       </c>
       <c r="G398" s="14" t="inlineStr">
         <is>
-          <t>Timing at 0.50× pickup</t>
+          <t>Timing at 0.5× pickup</t>
         </is>
       </c>
       <c r="H398" s="15" t="n"/>
@@ -39914,7 +39958,7 @@
       </c>
       <c r="G399" s="14" t="inlineStr">
         <is>
-          <t>Timing at 0.50× pickup</t>
+          <t>Timing at 0.5× pickup</t>
         </is>
       </c>
       <c r="H399" s="15" t="n"/>
